--- a/media/esclerometria/Tabela_Esclerometria - Hydro Silo.xlsx
+++ b/media/esclerometria/Tabela_Esclerometria - Hydro Silo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e14ca4ed5cbd9145/myWebSitesVScode/espEngFerrovIntegrPontes/parte01_END_concr/ppt/media/esclerometria/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e14ca4ed5cbd9145/myWebSitesVScode/espEngFerrovIntegrPontes/parte01_END_concr/media/esclerometria/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{DAABC195-199E-4726-BC15-E504CCFF2D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46052672-884C-4093-9290-4AF9CE6B1B5D}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{9A746B6E-5B14-49D6-94F2-6D86E29A27E7}"/>
+    <workbookView minimized="1" xWindow="32205" yWindow="3735" windowWidth="17280" windowHeight="8880" activeTab="5" xr2:uid="{9A746B6E-5B14-49D6-94F2-6D86E29A27E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Table1" sheetId="2" r:id="rId1"/>
@@ -21,38 +21,6 @@
     <sheet name="Sheet1 (2)" sheetId="8" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$E$51:$E$79</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$F$51:$F$79</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$O$51:$O$79</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$P$51:$P$79</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$Q$51:$Q$79</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$R$51:$R$79</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$S$51:$S$79</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$T$51:$T$79</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$E$51:$E$79</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$F$51:$F$79</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$G$51:$G$79</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$H$51:$H$79</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$G$51:$G$79</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$I$51:$I$79</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$J$51:$J$79</definedName>
-    <definedName name="_xlchart.v1.22" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$K$51:$K$79</definedName>
-    <definedName name="_xlchart.v1.23" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$L$51:$L$79</definedName>
-    <definedName name="_xlchart.v1.24" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$M$51:$M$79</definedName>
-    <definedName name="_xlchart.v1.25" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$N$51:$N$79</definedName>
-    <definedName name="_xlchart.v1.26" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$O$51:$O$79</definedName>
-    <definedName name="_xlchart.v1.27" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$P$51:$P$79</definedName>
-    <definedName name="_xlchart.v1.28" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$Q$51:$Q$79</definedName>
-    <definedName name="_xlchart.v1.29" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$R$51:$R$79</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$H$51:$H$79</definedName>
-    <definedName name="_xlchart.v1.30" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$S$51:$S$79</definedName>
-    <definedName name="_xlchart.v1.31" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$T$51:$T$79</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$I$51:$I$79</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$J$51:$J$79</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$K$51:$K$79</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$L$51:$L$79</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$M$51:$M$79</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">'TABELA_ESCLEROMETRIA REV (2)'!$N$51:$N$79</definedName>
     <definedName name="ExternalData_1" localSheetId="0" hidden="1">Table1!$A$1:$B$23</definedName>
     <definedName name="ExternalData_1" localSheetId="1" hidden="1">Table3!$A$1:$B$16</definedName>
   </definedNames>
@@ -1758,24 +1726,6 @@
     <xf numFmtId="2" fontId="6" fillId="7" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1908,6 +1858,24 @@
     <xf numFmtId="2" fontId="4" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1924,13 +1892,6 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
         <patternFill patternType="solid">
           <fgColor auto="1"/>
           <bgColor rgb="FFFF00FF"/>
@@ -1942,6 +1903,13 @@
         <patternFill patternType="solid">
           <fgColor auto="1"/>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1978,8 +1946,9 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFFF00FF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1993,9 +1962,16 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFFF00FF"/>
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2004,14 +1980,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FF00B0F0"/>
           <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6264,6 +6232,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{00000000-0016-0000-0000-000000000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="3">
@@ -8485,40 +8457,40 @@
   <sheetData>
     <row r="1" spans="4:32" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="4:32" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D2" s="105" t="s">
+      <c r="D2" s="149" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="107" t="s">
+      <c r="E2" s="151" t="s">
         <v>137</v>
       </c>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
-      <c r="I2" s="108"/>
-      <c r="J2" s="108"/>
-      <c r="K2" s="108"/>
-      <c r="L2" s="108"/>
-      <c r="M2" s="108"/>
-      <c r="N2" s="108"/>
-      <c r="O2" s="108"/>
-      <c r="P2" s="108"/>
-      <c r="Q2" s="108"/>
-      <c r="R2" s="108"/>
-      <c r="S2" s="108"/>
-      <c r="T2" s="109"/>
-      <c r="U2" s="107" t="s">
+      <c r="F2" s="152"/>
+      <c r="G2" s="152"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="152"/>
+      <c r="K2" s="152"/>
+      <c r="L2" s="152"/>
+      <c r="M2" s="152"/>
+      <c r="N2" s="152"/>
+      <c r="O2" s="152"/>
+      <c r="P2" s="152"/>
+      <c r="Q2" s="152"/>
+      <c r="R2" s="152"/>
+      <c r="S2" s="152"/>
+      <c r="T2" s="153"/>
+      <c r="U2" s="151" t="s">
         <v>1</v>
       </c>
-      <c r="V2" s="108"/>
-      <c r="W2" s="109"/>
-      <c r="X2" s="107" t="s">
+      <c r="V2" s="152"/>
+      <c r="W2" s="153"/>
+      <c r="X2" s="151" t="s">
         <v>2</v>
       </c>
-      <c r="Y2" s="108"/>
-      <c r="Z2" s="109"/>
+      <c r="Y2" s="152"/>
+      <c r="Z2" s="153"/>
     </row>
     <row r="3" spans="4:32" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D3" s="106"/>
+      <c r="D3" s="150"/>
       <c r="E3" s="74">
         <v>1</v>
       </c>
@@ -12366,37 +12338,37 @@
       </c>
     </row>
     <row r="49" spans="4:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D49" s="110" t="s">
+      <c r="D49" s="154" t="s">
         <v>0</v>
       </c>
-      <c r="E49" s="111" t="s">
+      <c r="E49" s="156" t="s">
         <v>137</v>
       </c>
-      <c r="F49" s="112"/>
-      <c r="G49" s="112"/>
-      <c r="H49" s="112"/>
-      <c r="I49" s="112"/>
-      <c r="J49" s="112"/>
-      <c r="K49" s="112"/>
-      <c r="L49" s="112"/>
-      <c r="M49" s="112"/>
-      <c r="N49" s="112"/>
-      <c r="O49" s="112"/>
-      <c r="P49" s="112"/>
-      <c r="Q49" s="112"/>
-      <c r="R49" s="112"/>
-      <c r="S49" s="112"/>
-      <c r="T49" s="113"/>
-      <c r="U49" s="111" t="s">
+      <c r="F49" s="157"/>
+      <c r="G49" s="157"/>
+      <c r="H49" s="157"/>
+      <c r="I49" s="157"/>
+      <c r="J49" s="157"/>
+      <c r="K49" s="157"/>
+      <c r="L49" s="157"/>
+      <c r="M49" s="157"/>
+      <c r="N49" s="157"/>
+      <c r="O49" s="157"/>
+      <c r="P49" s="157"/>
+      <c r="Q49" s="157"/>
+      <c r="R49" s="157"/>
+      <c r="S49" s="157"/>
+      <c r="T49" s="158"/>
+      <c r="U49" s="156" t="s">
         <v>1</v>
       </c>
-      <c r="V49" s="112"/>
-      <c r="W49" s="113"/>
-      <c r="X49" s="111" t="s">
+      <c r="V49" s="157"/>
+      <c r="W49" s="158"/>
+      <c r="X49" s="156" t="s">
         <v>2</v>
       </c>
-      <c r="Y49" s="112"/>
-      <c r="Z49" s="113"/>
+      <c r="Y49" s="157"/>
+      <c r="Z49" s="158"/>
       <c r="AC49" s="27">
         <v>34</v>
       </c>
@@ -12408,2303 +12380,2303 @@
       </c>
     </row>
     <row r="50" spans="4:31" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D50" s="114"/>
-      <c r="E50" s="115">
+      <c r="D50" s="155"/>
+      <c r="E50" s="105">
         <v>1</v>
       </c>
-      <c r="F50" s="116">
+      <c r="F50" s="106">
         <v>2</v>
       </c>
-      <c r="G50" s="116">
+      <c r="G50" s="106">
         <v>3</v>
       </c>
-      <c r="H50" s="116">
+      <c r="H50" s="106">
         <v>4</v>
       </c>
-      <c r="I50" s="116">
+      <c r="I50" s="106">
         <v>5</v>
       </c>
-      <c r="J50" s="116">
+      <c r="J50" s="106">
         <v>6</v>
       </c>
-      <c r="K50" s="116">
+      <c r="K50" s="106">
         <v>7</v>
       </c>
-      <c r="L50" s="116">
+      <c r="L50" s="106">
         <v>8</v>
       </c>
-      <c r="M50" s="116">
+      <c r="M50" s="106">
         <v>9</v>
       </c>
-      <c r="N50" s="116">
+      <c r="N50" s="106">
         <v>10</v>
       </c>
-      <c r="O50" s="116">
+      <c r="O50" s="106">
         <v>11</v>
       </c>
-      <c r="P50" s="116">
+      <c r="P50" s="106">
         <v>12</v>
       </c>
-      <c r="Q50" s="116">
+      <c r="Q50" s="106">
         <v>13</v>
       </c>
-      <c r="R50" s="116">
+      <c r="R50" s="106">
         <v>14</v>
       </c>
-      <c r="S50" s="116">
+      <c r="S50" s="106">
         <v>15</v>
       </c>
-      <c r="T50" s="117">
+      <c r="T50" s="107">
         <v>16</v>
       </c>
-      <c r="U50" s="118" t="s">
+      <c r="U50" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="V50" s="119" t="s">
+      <c r="V50" s="109" t="s">
         <v>4</v>
       </c>
-      <c r="W50" s="120" t="s">
+      <c r="W50" s="110" t="s">
         <v>5</v>
       </c>
-      <c r="X50" s="118" t="s">
+      <c r="X50" s="108" t="s">
         <v>6</v>
       </c>
-      <c r="Y50" s="119" t="s">
+      <c r="Y50" s="109" t="s">
         <v>4</v>
       </c>
-      <c r="Z50" s="120" t="s">
+      <c r="Z50" s="110" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="51" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D51" s="121" t="s">
+      <c r="D51" s="111" t="s">
         <v>10</v>
       </c>
-      <c r="E51" s="142">
-        <v>30</v>
-      </c>
-      <c r="F51" s="143">
+      <c r="E51" s="132">
+        <v>30</v>
+      </c>
+      <c r="F51" s="133">
         <v>32</v>
       </c>
-      <c r="G51" s="143">
+      <c r="G51" s="133">
         <v>32</v>
       </c>
-      <c r="H51" s="143">
+      <c r="H51" s="133">
         <v>33</v>
       </c>
-      <c r="I51" s="143">
+      <c r="I51" s="133">
         <v>34</v>
       </c>
-      <c r="J51" s="143">
+      <c r="J51" s="133">
         <v>34</v>
       </c>
-      <c r="K51" s="143">
+      <c r="K51" s="133">
         <v>35</v>
       </c>
-      <c r="L51" s="143">
+      <c r="L51" s="133">
         <v>36</v>
       </c>
-      <c r="M51" s="143">
+      <c r="M51" s="133">
         <v>36</v>
       </c>
-      <c r="N51" s="143">
+      <c r="N51" s="133">
         <v>36</v>
       </c>
-      <c r="O51" s="143">
+      <c r="O51" s="133">
         <v>36</v>
       </c>
-      <c r="P51" s="143">
+      <c r="P51" s="133">
         <v>36</v>
       </c>
-      <c r="Q51" s="143">
+      <c r="Q51" s="133">
         <v>36</v>
       </c>
-      <c r="R51" s="143">
+      <c r="R51" s="133">
         <v>37</v>
       </c>
-      <c r="S51" s="143">
+      <c r="S51" s="133">
         <v>37</v>
       </c>
-      <c r="T51" s="144">
+      <c r="T51" s="134">
         <v>37</v>
       </c>
-      <c r="U51" s="151">
+      <c r="U51" s="141">
         <f t="shared" ref="U51:U66" si="9">AVERAGE(E51:T51)</f>
         <v>34.8125</v>
       </c>
-      <c r="V51" s="126">
+      <c r="V51" s="116">
         <f t="shared" ref="V51:V72" si="10">U51*0.9</f>
         <v>31.331250000000001</v>
       </c>
-      <c r="W51" s="127">
+      <c r="W51" s="117">
         <f t="shared" ref="W51:W72" si="11">U51*1.1</f>
         <v>38.293750000000003</v>
       </c>
-      <c r="X51" s="155">
+      <c r="X51" s="145">
         <f t="shared" ref="X51:X66" si="12">AVERAGEIFS(E51:T51,E51:T51,"&gt;"&amp;V51, E51:T51, "&lt;"&amp;W51)</f>
         <v>35.133333333333333</v>
       </c>
-      <c r="Y51" s="128">
+      <c r="Y51" s="118">
         <f t="shared" ref="Y51:Y72" si="13">X51*0.9</f>
         <v>31.62</v>
       </c>
-      <c r="Z51" s="129">
+      <c r="Z51" s="119">
         <f t="shared" ref="Z51:Z88" si="14">X51*1.1</f>
         <v>38.646666666666668</v>
       </c>
     </row>
     <row r="52" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D52" s="122" t="s">
+      <c r="D52" s="112" t="s">
         <v>11</v>
       </c>
-      <c r="E52" s="145">
-        <v>30</v>
-      </c>
-      <c r="F52" s="146">
-        <v>30</v>
-      </c>
-      <c r="G52" s="146">
-        <v>30</v>
-      </c>
-      <c r="H52" s="146">
-        <v>30</v>
-      </c>
-      <c r="I52" s="146">
-        <v>30</v>
-      </c>
-      <c r="J52" s="146">
-        <v>30</v>
-      </c>
-      <c r="K52" s="146">
+      <c r="E52" s="135">
+        <v>30</v>
+      </c>
+      <c r="F52" s="136">
+        <v>30</v>
+      </c>
+      <c r="G52" s="136">
+        <v>30</v>
+      </c>
+      <c r="H52" s="136">
+        <v>30</v>
+      </c>
+      <c r="I52" s="136">
+        <v>30</v>
+      </c>
+      <c r="J52" s="136">
+        <v>30</v>
+      </c>
+      <c r="K52" s="136">
         <v>31</v>
       </c>
-      <c r="L52" s="146">
+      <c r="L52" s="136">
         <v>31</v>
       </c>
-      <c r="M52" s="146">
+      <c r="M52" s="136">
         <v>31</v>
       </c>
-      <c r="N52" s="146">
+      <c r="N52" s="136">
         <v>31</v>
       </c>
-      <c r="O52" s="146">
+      <c r="O52" s="136">
         <v>32</v>
       </c>
-      <c r="P52" s="146">
+      <c r="P52" s="136">
         <v>32</v>
       </c>
-      <c r="Q52" s="146">
+      <c r="Q52" s="136">
         <v>32</v>
       </c>
-      <c r="R52" s="146">
+      <c r="R52" s="136">
         <v>32</v>
       </c>
-      <c r="S52" s="146">
+      <c r="S52" s="136">
         <v>32</v>
       </c>
-      <c r="T52" s="147">
+      <c r="T52" s="137">
         <v>32</v>
       </c>
-      <c r="U52" s="152">
+      <c r="U52" s="142">
         <f t="shared" si="9"/>
         <v>31</v>
       </c>
-      <c r="V52" s="130">
+      <c r="V52" s="120">
         <f t="shared" si="10"/>
         <v>27.900000000000002</v>
       </c>
-      <c r="W52" s="131">
+      <c r="W52" s="121">
         <f t="shared" si="11"/>
         <v>34.1</v>
       </c>
-      <c r="X52" s="156">
+      <c r="X52" s="146">
         <f t="shared" si="12"/>
         <v>31</v>
       </c>
-      <c r="Y52" s="132">
+      <c r="Y52" s="122">
         <f t="shared" si="13"/>
         <v>27.900000000000002</v>
       </c>
-      <c r="Z52" s="133">
+      <c r="Z52" s="123">
         <f t="shared" si="14"/>
         <v>34.1</v>
       </c>
     </row>
     <row r="53" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D53" s="122" t="s">
+      <c r="D53" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="E53" s="145">
+      <c r="E53" s="135">
         <v>27</v>
       </c>
-      <c r="F53" s="146">
-        <v>30</v>
-      </c>
-      <c r="G53" s="146">
+      <c r="F53" s="136">
+        <v>30</v>
+      </c>
+      <c r="G53" s="136">
         <v>31</v>
       </c>
-      <c r="H53" s="146">
+      <c r="H53" s="136">
         <v>31</v>
       </c>
-      <c r="I53" s="146">
+      <c r="I53" s="136">
         <v>31</v>
       </c>
-      <c r="J53" s="146">
+      <c r="J53" s="136">
         <v>31</v>
       </c>
-      <c r="K53" s="146">
+      <c r="K53" s="136">
         <v>32</v>
       </c>
-      <c r="L53" s="146">
+      <c r="L53" s="136">
         <v>32</v>
       </c>
-      <c r="M53" s="146">
+      <c r="M53" s="136">
         <v>32</v>
       </c>
-      <c r="N53" s="146">
+      <c r="N53" s="136">
         <v>33</v>
       </c>
-      <c r="O53" s="146">
+      <c r="O53" s="136">
         <v>33</v>
       </c>
-      <c r="P53" s="146">
+      <c r="P53" s="136">
         <v>34</v>
       </c>
-      <c r="Q53" s="146">
+      <c r="Q53" s="136">
         <v>34</v>
       </c>
-      <c r="R53" s="146">
+      <c r="R53" s="136">
         <v>37</v>
       </c>
-      <c r="S53" s="146">
+      <c r="S53" s="136">
         <v>39</v>
       </c>
-      <c r="T53" s="147">
+      <c r="T53" s="137">
         <v>39</v>
       </c>
-      <c r="U53" s="152">
+      <c r="U53" s="142">
         <f t="shared" si="9"/>
         <v>32.875</v>
       </c>
-      <c r="V53" s="130">
+      <c r="V53" s="120">
         <f t="shared" si="10"/>
         <v>29.587500000000002</v>
       </c>
-      <c r="W53" s="131">
+      <c r="W53" s="121">
         <f t="shared" si="11"/>
         <v>36.162500000000001</v>
       </c>
-      <c r="X53" s="156">
+      <c r="X53" s="146">
         <f t="shared" si="12"/>
         <v>32</v>
       </c>
-      <c r="Y53" s="132">
+      <c r="Y53" s="122">
         <f t="shared" si="13"/>
         <v>28.8</v>
       </c>
-      <c r="Z53" s="133">
+      <c r="Z53" s="123">
         <f t="shared" si="14"/>
         <v>35.200000000000003</v>
       </c>
     </row>
     <row r="54" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D54" s="122" t="s">
+      <c r="D54" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="E54" s="145">
+      <c r="E54" s="135">
         <v>33</v>
       </c>
-      <c r="F54" s="146">
+      <c r="F54" s="136">
         <v>33</v>
       </c>
-      <c r="G54" s="146">
+      <c r="G54" s="136">
         <v>34</v>
       </c>
-      <c r="H54" s="146">
+      <c r="H54" s="136">
         <v>34</v>
       </c>
-      <c r="I54" s="146">
+      <c r="I54" s="136">
         <v>36</v>
       </c>
-      <c r="J54" s="146">
+      <c r="J54" s="136">
         <v>36</v>
       </c>
-      <c r="K54" s="146">
+      <c r="K54" s="136">
         <v>37</v>
       </c>
-      <c r="L54" s="146">
+      <c r="L54" s="136">
         <v>37</v>
       </c>
-      <c r="M54" s="146">
+      <c r="M54" s="136">
         <v>37</v>
       </c>
-      <c r="N54" s="146">
+      <c r="N54" s="136">
         <v>37</v>
       </c>
-      <c r="O54" s="146">
+      <c r="O54" s="136">
         <v>38</v>
       </c>
-      <c r="P54" s="146">
+      <c r="P54" s="136">
         <v>38</v>
       </c>
-      <c r="Q54" s="146">
+      <c r="Q54" s="136">
         <v>39</v>
       </c>
-      <c r="R54" s="146">
+      <c r="R54" s="136">
         <v>39</v>
       </c>
-      <c r="S54" s="146">
+      <c r="S54" s="136">
         <v>40</v>
       </c>
-      <c r="T54" s="147">
+      <c r="T54" s="137">
         <v>48</v>
       </c>
-      <c r="U54" s="152">
+      <c r="U54" s="142">
         <f t="shared" si="9"/>
         <v>37.25</v>
       </c>
-      <c r="V54" s="130">
+      <c r="V54" s="120">
         <f t="shared" si="10"/>
         <v>33.524999999999999</v>
       </c>
-      <c r="W54" s="131">
+      <c r="W54" s="121">
         <f t="shared" si="11"/>
         <v>40.975000000000001</v>
       </c>
-      <c r="X54" s="156">
+      <c r="X54" s="146">
         <f t="shared" si="12"/>
         <v>37.07692307692308</v>
       </c>
-      <c r="Y54" s="132">
+      <c r="Y54" s="122">
         <f t="shared" si="13"/>
         <v>33.369230769230775</v>
       </c>
-      <c r="Z54" s="133">
+      <c r="Z54" s="123">
         <f t="shared" si="14"/>
         <v>40.784615384615392</v>
       </c>
     </row>
     <row r="55" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D55" s="122" t="s">
+      <c r="D55" s="112" t="s">
         <v>14</v>
       </c>
-      <c r="E55" s="145">
+      <c r="E55" s="135">
         <v>31</v>
       </c>
-      <c r="F55" s="146">
+      <c r="F55" s="136">
         <v>34</v>
       </c>
-      <c r="G55" s="146">
+      <c r="G55" s="136">
         <v>34</v>
       </c>
-      <c r="H55" s="146">
+      <c r="H55" s="136">
         <v>35</v>
       </c>
-      <c r="I55" s="146">
+      <c r="I55" s="136">
         <v>35</v>
       </c>
-      <c r="J55" s="146">
+      <c r="J55" s="136">
         <v>36</v>
       </c>
-      <c r="K55" s="146">
+      <c r="K55" s="136">
         <v>36</v>
       </c>
-      <c r="L55" s="146">
+      <c r="L55" s="136">
         <v>36</v>
       </c>
-      <c r="M55" s="146">
+      <c r="M55" s="136">
         <v>36</v>
       </c>
-      <c r="N55" s="146">
+      <c r="N55" s="136">
         <v>38</v>
       </c>
-      <c r="O55" s="146">
+      <c r="O55" s="136">
         <v>38</v>
       </c>
-      <c r="P55" s="146">
+      <c r="P55" s="136">
         <v>38</v>
       </c>
-      <c r="Q55" s="146">
+      <c r="Q55" s="136">
         <v>38</v>
       </c>
-      <c r="R55" s="146">
+      <c r="R55" s="136">
         <v>39</v>
       </c>
-      <c r="S55" s="146">
+      <c r="S55" s="136">
         <v>44</v>
       </c>
-      <c r="T55" s="147">
+      <c r="T55" s="137">
         <v>48</v>
       </c>
-      <c r="U55" s="152">
+      <c r="U55" s="142">
         <f t="shared" si="9"/>
         <v>37.25</v>
       </c>
-      <c r="V55" s="130">
+      <c r="V55" s="120">
         <f t="shared" si="10"/>
         <v>33.524999999999999</v>
       </c>
-      <c r="W55" s="131">
+      <c r="W55" s="121">
         <f t="shared" si="11"/>
         <v>40.975000000000001</v>
       </c>
-      <c r="X55" s="156">
+      <c r="X55" s="146">
         <f t="shared" si="12"/>
         <v>36.384615384615387</v>
       </c>
-      <c r="Y55" s="132">
+      <c r="Y55" s="122">
         <f t="shared" si="13"/>
         <v>32.746153846153852</v>
       </c>
-      <c r="Z55" s="133">
+      <c r="Z55" s="123">
         <f t="shared" si="14"/>
         <v>40.023076923076928</v>
       </c>
     </row>
     <row r="56" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D56" s="122" t="s">
+      <c r="D56" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="E56" s="145">
+      <c r="E56" s="135">
         <v>35</v>
       </c>
-      <c r="F56" s="146">
+      <c r="F56" s="136">
         <v>35</v>
       </c>
-      <c r="G56" s="146">
+      <c r="G56" s="136">
         <v>36</v>
       </c>
-      <c r="H56" s="146">
+      <c r="H56" s="136">
         <v>36</v>
       </c>
-      <c r="I56" s="146">
+      <c r="I56" s="136">
         <v>37</v>
       </c>
-      <c r="J56" s="146">
+      <c r="J56" s="136">
         <v>38</v>
       </c>
-      <c r="K56" s="146">
+      <c r="K56" s="136">
         <v>38</v>
       </c>
-      <c r="L56" s="146">
+      <c r="L56" s="136">
         <v>38</v>
       </c>
-      <c r="M56" s="146">
+      <c r="M56" s="136">
         <v>41</v>
       </c>
-      <c r="N56" s="146">
+      <c r="N56" s="136">
         <v>41</v>
       </c>
-      <c r="O56" s="146">
+      <c r="O56" s="136">
         <v>42</v>
       </c>
-      <c r="P56" s="146">
+      <c r="P56" s="136">
         <v>42</v>
       </c>
-      <c r="Q56" s="146">
+      <c r="Q56" s="136">
         <v>44</v>
       </c>
-      <c r="R56" s="146">
+      <c r="R56" s="136">
         <v>45</v>
       </c>
-      <c r="S56" s="146">
+      <c r="S56" s="136">
         <v>53</v>
       </c>
-      <c r="T56" s="147">
+      <c r="T56" s="137">
         <v>58</v>
       </c>
-      <c r="U56" s="152">
+      <c r="U56" s="142">
         <f t="shared" si="9"/>
         <v>41.1875</v>
       </c>
-      <c r="V56" s="130">
+      <c r="V56" s="120">
         <f t="shared" si="10"/>
         <v>37.068750000000001</v>
       </c>
-      <c r="W56" s="131">
+      <c r="W56" s="121">
         <f t="shared" si="11"/>
         <v>45.306250000000006</v>
       </c>
-      <c r="X56" s="156">
+      <c r="X56" s="146">
         <f t="shared" si="12"/>
         <v>41</v>
       </c>
-      <c r="Y56" s="132">
+      <c r="Y56" s="122">
         <f t="shared" si="13"/>
         <v>36.9</v>
       </c>
-      <c r="Z56" s="133">
+      <c r="Z56" s="123">
         <f t="shared" si="14"/>
         <v>45.1</v>
       </c>
     </row>
     <row r="57" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D57" s="122" t="s">
+      <c r="D57" s="112" t="s">
         <v>16</v>
       </c>
-      <c r="E57" s="145">
+      <c r="E57" s="135">
         <v>31</v>
       </c>
-      <c r="F57" s="146">
+      <c r="F57" s="136">
         <v>35</v>
       </c>
-      <c r="G57" s="146">
+      <c r="G57" s="136">
         <v>36</v>
       </c>
-      <c r="H57" s="146">
+      <c r="H57" s="136">
         <v>36</v>
       </c>
-      <c r="I57" s="146">
+      <c r="I57" s="136">
         <v>37</v>
       </c>
-      <c r="J57" s="146">
+      <c r="J57" s="136">
         <v>37</v>
       </c>
-      <c r="K57" s="146">
+      <c r="K57" s="136">
         <v>38</v>
       </c>
-      <c r="L57" s="146">
+      <c r="L57" s="136">
         <v>38</v>
       </c>
-      <c r="M57" s="146">
+      <c r="M57" s="136">
         <v>38</v>
       </c>
-      <c r="N57" s="146">
+      <c r="N57" s="136">
         <v>39</v>
       </c>
-      <c r="O57" s="146">
+      <c r="O57" s="136">
         <v>39</v>
       </c>
-      <c r="P57" s="146">
+      <c r="P57" s="136">
         <v>40</v>
       </c>
-      <c r="Q57" s="146">
+      <c r="Q57" s="136">
         <v>41</v>
       </c>
-      <c r="R57" s="146">
+      <c r="R57" s="136">
         <v>41</v>
       </c>
-      <c r="S57" s="146">
+      <c r="S57" s="136">
         <v>45</v>
       </c>
-      <c r="T57" s="147">
+      <c r="T57" s="137">
         <v>46</v>
       </c>
-      <c r="U57" s="152">
+      <c r="U57" s="142">
         <f t="shared" si="9"/>
         <v>38.5625</v>
       </c>
-      <c r="V57" s="130">
+      <c r="V57" s="120">
         <f t="shared" si="10"/>
         <v>34.706250000000004</v>
       </c>
-      <c r="W57" s="131">
+      <c r="W57" s="121">
         <f t="shared" si="11"/>
         <v>42.418750000000003</v>
       </c>
-      <c r="X57" s="156">
+      <c r="X57" s="146">
         <f t="shared" si="12"/>
         <v>38.07692307692308</v>
       </c>
-      <c r="Y57" s="132">
+      <c r="Y57" s="122">
         <f t="shared" si="13"/>
         <v>34.269230769230774</v>
       </c>
-      <c r="Z57" s="133">
+      <c r="Z57" s="123">
         <f t="shared" si="14"/>
         <v>41.884615384615394</v>
       </c>
     </row>
     <row r="58" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D58" s="122" t="s">
+      <c r="D58" s="112" t="s">
         <v>17</v>
       </c>
-      <c r="E58" s="145">
+      <c r="E58" s="135">
         <v>26</v>
       </c>
-      <c r="F58" s="146">
+      <c r="F58" s="136">
         <v>27</v>
       </c>
-      <c r="G58" s="146">
+      <c r="G58" s="136">
         <v>28</v>
       </c>
-      <c r="H58" s="146">
+      <c r="H58" s="136">
         <v>29</v>
       </c>
-      <c r="I58" s="146">
-        <v>30</v>
-      </c>
-      <c r="J58" s="146">
-        <v>30</v>
-      </c>
-      <c r="K58" s="146">
+      <c r="I58" s="136">
+        <v>30</v>
+      </c>
+      <c r="J58" s="136">
+        <v>30</v>
+      </c>
+      <c r="K58" s="136">
         <v>32</v>
       </c>
-      <c r="L58" s="146">
+      <c r="L58" s="136">
         <v>32</v>
       </c>
-      <c r="M58" s="146">
+      <c r="M58" s="136">
         <v>32</v>
       </c>
-      <c r="N58" s="146">
+      <c r="N58" s="136">
         <v>33</v>
       </c>
-      <c r="O58" s="146">
+      <c r="O58" s="136">
         <v>33</v>
       </c>
-      <c r="P58" s="146">
+      <c r="P58" s="136">
         <v>34</v>
       </c>
-      <c r="Q58" s="146">
+      <c r="Q58" s="136">
         <v>35</v>
       </c>
-      <c r="R58" s="146">
+      <c r="R58" s="136">
         <v>36</v>
       </c>
-      <c r="S58" s="146">
+      <c r="S58" s="136">
         <v>36</v>
       </c>
-      <c r="T58" s="147">
+      <c r="T58" s="137">
         <v>37</v>
       </c>
-      <c r="U58" s="152">
+      <c r="U58" s="142">
         <f t="shared" si="9"/>
         <v>31.875</v>
       </c>
-      <c r="V58" s="130">
+      <c r="V58" s="120">
         <f t="shared" si="10"/>
         <v>28.6875</v>
       </c>
-      <c r="W58" s="131">
+      <c r="W58" s="121">
         <f t="shared" si="11"/>
         <v>35.0625</v>
       </c>
-      <c r="X58" s="156">
+      <c r="X58" s="146">
         <f t="shared" si="12"/>
         <v>32</v>
       </c>
-      <c r="Y58" s="132">
+      <c r="Y58" s="122">
         <f t="shared" si="13"/>
         <v>28.8</v>
       </c>
-      <c r="Z58" s="133">
+      <c r="Z58" s="123">
         <f t="shared" si="14"/>
         <v>35.200000000000003</v>
       </c>
     </row>
     <row r="59" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D59" s="122" t="s">
+      <c r="D59" s="112" t="s">
         <v>18</v>
       </c>
-      <c r="E59" s="145">
+      <c r="E59" s="135">
         <v>29</v>
       </c>
-      <c r="F59" s="146">
-        <v>30</v>
-      </c>
-      <c r="G59" s="146">
-        <v>30</v>
-      </c>
-      <c r="H59" s="146">
-        <v>30</v>
-      </c>
-      <c r="I59" s="146">
-        <v>30</v>
-      </c>
-      <c r="J59" s="146">
+      <c r="F59" s="136">
+        <v>30</v>
+      </c>
+      <c r="G59" s="136">
+        <v>30</v>
+      </c>
+      <c r="H59" s="136">
+        <v>30</v>
+      </c>
+      <c r="I59" s="136">
+        <v>30</v>
+      </c>
+      <c r="J59" s="136">
         <v>31</v>
       </c>
-      <c r="K59" s="146">
+      <c r="K59" s="136">
         <v>31</v>
       </c>
-      <c r="L59" s="146">
+      <c r="L59" s="136">
         <v>32</v>
       </c>
-      <c r="M59" s="146">
+      <c r="M59" s="136">
         <v>32</v>
       </c>
-      <c r="N59" s="146">
+      <c r="N59" s="136">
         <v>32</v>
       </c>
-      <c r="O59" s="146">
+      <c r="O59" s="136">
         <v>33</v>
       </c>
-      <c r="P59" s="146">
+      <c r="P59" s="136">
         <v>34</v>
       </c>
-      <c r="Q59" s="146">
+      <c r="Q59" s="136">
         <v>35</v>
       </c>
-      <c r="R59" s="146">
+      <c r="R59" s="136">
         <v>35</v>
       </c>
-      <c r="S59" s="146">
+      <c r="S59" s="136">
         <v>36</v>
       </c>
-      <c r="T59" s="147">
+      <c r="T59" s="137">
         <v>36</v>
       </c>
-      <c r="U59" s="152">
+      <c r="U59" s="142">
         <f t="shared" si="9"/>
         <v>32.25</v>
       </c>
-      <c r="V59" s="130">
+      <c r="V59" s="120">
         <f t="shared" si="10"/>
         <v>29.025000000000002</v>
       </c>
-      <c r="W59" s="131">
+      <c r="W59" s="121">
         <f t="shared" si="11"/>
         <v>35.475000000000001</v>
       </c>
-      <c r="X59" s="156">
+      <c r="X59" s="146">
         <f t="shared" si="12"/>
         <v>31.923076923076923</v>
       </c>
-      <c r="Y59" s="132">
+      <c r="Y59" s="122">
         <f t="shared" si="13"/>
         <v>28.73076923076923</v>
       </c>
-      <c r="Z59" s="133">
+      <c r="Z59" s="123">
         <f t="shared" si="14"/>
         <v>35.11538461538462</v>
       </c>
     </row>
     <row r="60" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D60" s="122" t="s">
+      <c r="D60" s="112" t="s">
         <v>19</v>
       </c>
-      <c r="E60" s="145">
-        <v>30</v>
-      </c>
-      <c r="F60" s="146">
-        <v>30</v>
-      </c>
-      <c r="G60" s="146">
+      <c r="E60" s="135">
+        <v>30</v>
+      </c>
+      <c r="F60" s="136">
+        <v>30</v>
+      </c>
+      <c r="G60" s="136">
         <v>31</v>
       </c>
-      <c r="H60" s="146">
+      <c r="H60" s="136">
         <v>32</v>
       </c>
-      <c r="I60" s="146">
+      <c r="I60" s="136">
         <v>32</v>
       </c>
-      <c r="J60" s="146">
+      <c r="J60" s="136">
         <v>32</v>
       </c>
-      <c r="K60" s="146">
+      <c r="K60" s="136">
         <v>33</v>
       </c>
-      <c r="L60" s="146">
+      <c r="L60" s="136">
         <v>33</v>
       </c>
-      <c r="M60" s="146">
+      <c r="M60" s="136">
         <v>33</v>
       </c>
-      <c r="N60" s="146">
+      <c r="N60" s="136">
         <v>34</v>
       </c>
-      <c r="O60" s="146">
+      <c r="O60" s="136">
         <v>34</v>
       </c>
-      <c r="P60" s="146">
+      <c r="P60" s="136">
         <v>35</v>
       </c>
-      <c r="Q60" s="146">
+      <c r="Q60" s="136">
         <v>35</v>
       </c>
-      <c r="R60" s="146">
+      <c r="R60" s="136">
         <v>35</v>
       </c>
-      <c r="S60" s="146">
+      <c r="S60" s="136">
         <v>37</v>
       </c>
-      <c r="T60" s="147">
+      <c r="T60" s="137">
         <v>38</v>
       </c>
-      <c r="U60" s="152">
+      <c r="U60" s="142">
         <f t="shared" si="9"/>
         <v>33.375</v>
       </c>
-      <c r="V60" s="130">
+      <c r="V60" s="120">
         <f t="shared" si="10"/>
         <v>30.037500000000001</v>
       </c>
-      <c r="W60" s="131">
+      <c r="W60" s="121">
         <f t="shared" si="11"/>
         <v>36.712500000000006</v>
       </c>
-      <c r="X60" s="156">
+      <c r="X60" s="146">
         <f t="shared" si="12"/>
         <v>33.25</v>
       </c>
-      <c r="Y60" s="132">
+      <c r="Y60" s="122">
         <f t="shared" si="13"/>
         <v>29.925000000000001</v>
       </c>
-      <c r="Z60" s="133">
+      <c r="Z60" s="123">
         <f t="shared" si="14"/>
         <v>36.575000000000003</v>
       </c>
     </row>
     <row r="61" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D61" s="122" t="s">
+      <c r="D61" s="112" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="145">
-        <v>30</v>
-      </c>
-      <c r="F61" s="146">
-        <v>30</v>
-      </c>
-      <c r="G61" s="146">
+      <c r="E61" s="135">
+        <v>30</v>
+      </c>
+      <c r="F61" s="136">
+        <v>30</v>
+      </c>
+      <c r="G61" s="136">
         <v>31</v>
       </c>
-      <c r="H61" s="146">
+      <c r="H61" s="136">
         <v>32</v>
       </c>
-      <c r="I61" s="146">
+      <c r="I61" s="136">
         <v>32</v>
       </c>
-      <c r="J61" s="146">
+      <c r="J61" s="136">
         <v>32</v>
       </c>
-      <c r="K61" s="146">
+      <c r="K61" s="136">
         <v>33</v>
       </c>
-      <c r="L61" s="146">
+      <c r="L61" s="136">
         <v>33</v>
       </c>
-      <c r="M61" s="146">
+      <c r="M61" s="136">
         <v>33</v>
       </c>
-      <c r="N61" s="146">
+      <c r="N61" s="136">
         <v>33</v>
       </c>
-      <c r="O61" s="146">
+      <c r="O61" s="136">
         <v>34</v>
       </c>
-      <c r="P61" s="146">
+      <c r="P61" s="136">
         <v>34</v>
       </c>
-      <c r="Q61" s="146">
+      <c r="Q61" s="136">
         <v>34</v>
       </c>
-      <c r="R61" s="146">
+      <c r="R61" s="136">
         <v>34</v>
       </c>
-      <c r="S61" s="146">
+      <c r="S61" s="136">
         <v>37</v>
       </c>
-      <c r="T61" s="147">
+      <c r="T61" s="137">
         <v>39</v>
       </c>
-      <c r="U61" s="152">
+      <c r="U61" s="142">
         <f t="shared" si="9"/>
         <v>33.1875</v>
       </c>
-      <c r="V61" s="130">
+      <c r="V61" s="120">
         <f t="shared" si="10"/>
         <v>29.868750000000002</v>
       </c>
-      <c r="W61" s="131">
+      <c r="W61" s="121">
         <f t="shared" si="11"/>
         <v>36.506250000000001</v>
       </c>
-      <c r="X61" s="156">
+      <c r="X61" s="146">
         <f t="shared" si="12"/>
         <v>32.5</v>
       </c>
-      <c r="Y61" s="132">
+      <c r="Y61" s="122">
         <f t="shared" si="13"/>
         <v>29.25</v>
       </c>
-      <c r="Z61" s="133">
+      <c r="Z61" s="123">
         <f t="shared" si="14"/>
         <v>35.75</v>
       </c>
     </row>
     <row r="62" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D62" s="122" t="s">
+      <c r="D62" s="112" t="s">
         <v>21</v>
       </c>
-      <c r="E62" s="145">
+      <c r="E62" s="135">
         <v>28</v>
       </c>
-      <c r="F62" s="146">
-        <v>30</v>
-      </c>
-      <c r="G62" s="146">
-        <v>30</v>
-      </c>
-      <c r="H62" s="146">
-        <v>30</v>
-      </c>
-      <c r="I62" s="146">
-        <v>30</v>
-      </c>
-      <c r="J62" s="146">
+      <c r="F62" s="136">
+        <v>30</v>
+      </c>
+      <c r="G62" s="136">
+        <v>30</v>
+      </c>
+      <c r="H62" s="136">
+        <v>30</v>
+      </c>
+      <c r="I62" s="136">
+        <v>30</v>
+      </c>
+      <c r="J62" s="136">
         <v>32</v>
       </c>
-      <c r="K62" s="146">
+      <c r="K62" s="136">
         <v>32</v>
       </c>
-      <c r="L62" s="146">
+      <c r="L62" s="136">
         <v>32</v>
       </c>
-      <c r="M62" s="146">
+      <c r="M62" s="136">
         <v>32</v>
       </c>
-      <c r="N62" s="146">
+      <c r="N62" s="136">
         <v>32</v>
       </c>
-      <c r="O62" s="146">
+      <c r="O62" s="136">
         <v>32</v>
       </c>
-      <c r="P62" s="146">
+      <c r="P62" s="136">
         <v>33</v>
       </c>
-      <c r="Q62" s="146">
+      <c r="Q62" s="136">
         <v>33</v>
       </c>
-      <c r="R62" s="146">
+      <c r="R62" s="136">
         <v>37</v>
       </c>
-      <c r="S62" s="146">
+      <c r="S62" s="136">
         <v>39</v>
       </c>
-      <c r="T62" s="147">
+      <c r="T62" s="137">
         <v>40</v>
       </c>
-      <c r="U62" s="152">
+      <c r="U62" s="142">
         <f t="shared" si="9"/>
         <v>32.625</v>
       </c>
-      <c r="V62" s="130">
+      <c r="V62" s="120">
         <f t="shared" si="10"/>
         <v>29.362500000000001</v>
       </c>
-      <c r="W62" s="131">
+      <c r="W62" s="121">
         <f t="shared" si="11"/>
         <v>35.887500000000003</v>
       </c>
-      <c r="X62" s="156">
+      <c r="X62" s="146">
         <f t="shared" si="12"/>
         <v>31.5</v>
       </c>
-      <c r="Y62" s="132">
+      <c r="Y62" s="122">
         <f t="shared" si="13"/>
         <v>28.35</v>
       </c>
-      <c r="Z62" s="133">
+      <c r="Z62" s="123">
         <f t="shared" si="14"/>
         <v>34.650000000000006</v>
       </c>
     </row>
     <row r="63" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D63" s="122" t="s">
+      <c r="D63" s="112" t="s">
         <v>22</v>
       </c>
-      <c r="E63" s="145">
+      <c r="E63" s="135">
         <v>25</v>
       </c>
-      <c r="F63" s="146">
+      <c r="F63" s="136">
         <v>29</v>
       </c>
-      <c r="G63" s="146">
-        <v>30</v>
-      </c>
-      <c r="H63" s="146">
+      <c r="G63" s="136">
+        <v>30</v>
+      </c>
+      <c r="H63" s="136">
         <v>32</v>
       </c>
-      <c r="I63" s="146">
+      <c r="I63" s="136">
         <v>32</v>
       </c>
-      <c r="J63" s="146">
+      <c r="J63" s="136">
         <v>32</v>
       </c>
-      <c r="K63" s="146">
+      <c r="K63" s="136">
         <v>32</v>
       </c>
-      <c r="L63" s="146">
+      <c r="L63" s="136">
         <v>32</v>
       </c>
-      <c r="M63" s="146">
+      <c r="M63" s="136">
         <v>32</v>
       </c>
-      <c r="N63" s="146">
+      <c r="N63" s="136">
         <v>32</v>
       </c>
-      <c r="O63" s="146">
+      <c r="O63" s="136">
         <v>32</v>
       </c>
-      <c r="P63" s="146">
+      <c r="P63" s="136">
         <v>33</v>
       </c>
-      <c r="Q63" s="146">
+      <c r="Q63" s="136">
         <v>34</v>
       </c>
-      <c r="R63" s="146">
+      <c r="R63" s="136">
         <v>34</v>
       </c>
-      <c r="S63" s="146">
+      <c r="S63" s="136">
         <v>35</v>
       </c>
-      <c r="T63" s="147">
+      <c r="T63" s="137">
         <v>38</v>
       </c>
-      <c r="U63" s="152">
+      <c r="U63" s="142">
         <f t="shared" si="9"/>
         <v>32.125</v>
       </c>
-      <c r="V63" s="130">
+      <c r="V63" s="120">
         <f t="shared" si="10"/>
         <v>28.912500000000001</v>
       </c>
-      <c r="W63" s="131">
+      <c r="W63" s="121">
         <f t="shared" si="11"/>
         <v>35.337500000000006</v>
       </c>
-      <c r="X63" s="156">
+      <c r="X63" s="146">
         <f t="shared" si="12"/>
         <v>32.214285714285715</v>
       </c>
-      <c r="Y63" s="132">
+      <c r="Y63" s="122">
         <f t="shared" si="13"/>
         <v>28.992857142857144</v>
       </c>
-      <c r="Z63" s="133">
+      <c r="Z63" s="123">
         <f t="shared" si="14"/>
         <v>35.43571428571429</v>
       </c>
     </row>
     <row r="64" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D64" s="122" t="s">
+      <c r="D64" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="E64" s="145">
+      <c r="E64" s="135">
         <v>29</v>
       </c>
-      <c r="F64" s="146">
-        <v>30</v>
-      </c>
-      <c r="G64" s="146">
-        <v>30</v>
-      </c>
-      <c r="H64" s="146">
-        <v>30</v>
-      </c>
-      <c r="I64" s="146">
+      <c r="F64" s="136">
+        <v>30</v>
+      </c>
+      <c r="G64" s="136">
+        <v>30</v>
+      </c>
+      <c r="H64" s="136">
+        <v>30</v>
+      </c>
+      <c r="I64" s="136">
         <v>31</v>
       </c>
-      <c r="J64" s="146">
+      <c r="J64" s="136">
         <v>31</v>
       </c>
-      <c r="K64" s="146">
+      <c r="K64" s="136">
         <v>32</v>
       </c>
-      <c r="L64" s="146">
+      <c r="L64" s="136">
         <v>32</v>
       </c>
-      <c r="M64" s="146">
+      <c r="M64" s="136">
         <v>33</v>
       </c>
-      <c r="N64" s="146">
+      <c r="N64" s="136">
         <v>33</v>
       </c>
-      <c r="O64" s="146">
+      <c r="O64" s="136">
         <v>34</v>
       </c>
-      <c r="P64" s="146">
+      <c r="P64" s="136">
         <v>34</v>
       </c>
-      <c r="Q64" s="146">
+      <c r="Q64" s="136">
         <v>35</v>
       </c>
-      <c r="R64" s="146">
+      <c r="R64" s="136">
         <v>35</v>
       </c>
-      <c r="S64" s="146">
+      <c r="S64" s="136">
         <v>38</v>
       </c>
-      <c r="T64" s="147">
+      <c r="T64" s="137">
         <v>47</v>
       </c>
-      <c r="U64" s="152">
+      <c r="U64" s="142">
         <f t="shared" si="9"/>
         <v>33.375</v>
       </c>
-      <c r="V64" s="130">
+      <c r="V64" s="120">
         <f t="shared" si="10"/>
         <v>30.037500000000001</v>
       </c>
-      <c r="W64" s="131">
+      <c r="W64" s="121">
         <f t="shared" si="11"/>
         <v>36.712500000000006</v>
       </c>
-      <c r="X64" s="156">
+      <c r="X64" s="146">
         <f t="shared" si="12"/>
         <v>33</v>
       </c>
-      <c r="Y64" s="132">
+      <c r="Y64" s="122">
         <f t="shared" si="13"/>
         <v>29.7</v>
       </c>
-      <c r="Z64" s="133">
+      <c r="Z64" s="123">
         <f t="shared" si="14"/>
         <v>36.300000000000004</v>
       </c>
     </row>
     <row r="65" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D65" s="122" t="s">
+      <c r="D65" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="E65" s="145">
+      <c r="E65" s="135">
         <v>26</v>
       </c>
-      <c r="F65" s="146">
+      <c r="F65" s="136">
         <v>29</v>
       </c>
-      <c r="G65" s="146">
+      <c r="G65" s="136">
         <v>29</v>
       </c>
-      <c r="H65" s="146">
+      <c r="H65" s="136">
         <v>29</v>
       </c>
-      <c r="I65" s="146">
+      <c r="I65" s="136">
         <v>29</v>
       </c>
-      <c r="J65" s="146">
+      <c r="J65" s="136">
         <v>29</v>
       </c>
-      <c r="K65" s="146">
-        <v>30</v>
-      </c>
-      <c r="L65" s="146">
-        <v>30</v>
-      </c>
-      <c r="M65" s="146">
-        <v>30</v>
-      </c>
-      <c r="N65" s="146">
-        <v>30</v>
-      </c>
-      <c r="O65" s="146">
-        <v>30</v>
-      </c>
-      <c r="P65" s="146">
+      <c r="K65" s="136">
+        <v>30</v>
+      </c>
+      <c r="L65" s="136">
+        <v>30</v>
+      </c>
+      <c r="M65" s="136">
+        <v>30</v>
+      </c>
+      <c r="N65" s="136">
+        <v>30</v>
+      </c>
+      <c r="O65" s="136">
+        <v>30</v>
+      </c>
+      <c r="P65" s="136">
         <v>31</v>
       </c>
-      <c r="Q65" s="146">
+      <c r="Q65" s="136">
         <v>32</v>
       </c>
-      <c r="R65" s="146">
+      <c r="R65" s="136">
         <v>33</v>
       </c>
-      <c r="S65" s="146">
+      <c r="S65" s="136">
         <v>34</v>
       </c>
-      <c r="T65" s="147">
+      <c r="T65" s="137">
         <v>36</v>
       </c>
-      <c r="U65" s="152">
+      <c r="U65" s="142">
         <f t="shared" si="9"/>
         <v>30.4375</v>
       </c>
-      <c r="V65" s="130">
+      <c r="V65" s="120">
         <f t="shared" si="10"/>
         <v>27.393750000000001</v>
       </c>
-      <c r="W65" s="131">
+      <c r="W65" s="121">
         <f t="shared" si="11"/>
         <v>33.481250000000003</v>
       </c>
-      <c r="X65" s="156">
+      <c r="X65" s="146">
         <f t="shared" si="12"/>
         <v>30.076923076923077</v>
       </c>
-      <c r="Y65" s="132">
+      <c r="Y65" s="122">
         <f t="shared" si="13"/>
         <v>27.069230769230771</v>
       </c>
-      <c r="Z65" s="133">
+      <c r="Z65" s="123">
         <f t="shared" si="14"/>
         <v>33.08461538461539</v>
       </c>
     </row>
     <row r="66" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D66" s="122" t="s">
+      <c r="D66" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="E66" s="145">
-        <v>30</v>
-      </c>
-      <c r="F66" s="146">
+      <c r="E66" s="135">
+        <v>30</v>
+      </c>
+      <c r="F66" s="136">
         <v>31</v>
       </c>
-      <c r="G66" s="146">
+      <c r="G66" s="136">
         <v>32</v>
       </c>
-      <c r="H66" s="146">
+      <c r="H66" s="136">
         <v>32</v>
       </c>
-      <c r="I66" s="146">
+      <c r="I66" s="136">
         <v>33</v>
       </c>
-      <c r="J66" s="146">
+      <c r="J66" s="136">
         <v>33</v>
       </c>
-      <c r="K66" s="146">
+      <c r="K66" s="136">
         <v>34</v>
       </c>
-      <c r="L66" s="146">
+      <c r="L66" s="136">
         <v>34</v>
       </c>
-      <c r="M66" s="146">
+      <c r="M66" s="136">
         <v>34</v>
       </c>
-      <c r="N66" s="146">
+      <c r="N66" s="136">
         <v>34</v>
       </c>
-      <c r="O66" s="146">
+      <c r="O66" s="136">
         <v>35</v>
       </c>
-      <c r="P66" s="146">
+      <c r="P66" s="136">
         <v>35</v>
       </c>
-      <c r="Q66" s="146">
+      <c r="Q66" s="136">
         <v>36</v>
       </c>
-      <c r="R66" s="146">
+      <c r="R66" s="136">
         <v>37</v>
       </c>
-      <c r="S66" s="146">
+      <c r="S66" s="136">
         <v>38</v>
       </c>
-      <c r="T66" s="147">
+      <c r="T66" s="137">
         <v>45</v>
       </c>
-      <c r="U66" s="152">
+      <c r="U66" s="142">
         <f t="shared" si="9"/>
         <v>34.5625</v>
       </c>
-      <c r="V66" s="130">
+      <c r="V66" s="120">
         <f t="shared" si="10"/>
         <v>31.106249999999999</v>
       </c>
-      <c r="W66" s="131">
+      <c r="W66" s="121">
         <f t="shared" si="11"/>
         <v>38.018750000000004</v>
       </c>
-      <c r="X66" s="156">
+      <c r="X66" s="146">
         <f t="shared" si="12"/>
         <v>34.384615384615387</v>
       </c>
-      <c r="Y66" s="132">
+      <c r="Y66" s="122">
         <f t="shared" si="13"/>
         <v>30.946153846153848</v>
       </c>
-      <c r="Z66" s="133">
+      <c r="Z66" s="123">
         <f t="shared" si="14"/>
         <v>37.823076923076925</v>
       </c>
     </row>
     <row r="67" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D67" s="122" t="s">
+      <c r="D67" s="112" t="s">
         <v>26</v>
       </c>
-      <c r="E67" s="145">
+      <c r="E67" s="135">
         <v>29</v>
       </c>
-      <c r="F67" s="146">
+      <c r="F67" s="136">
         <v>31</v>
       </c>
-      <c r="G67" s="146">
+      <c r="G67" s="136">
         <v>31</v>
       </c>
-      <c r="H67" s="146">
+      <c r="H67" s="136">
         <v>31</v>
       </c>
-      <c r="I67" s="146">
+      <c r="I67" s="136">
         <v>31</v>
       </c>
-      <c r="J67" s="146">
+      <c r="J67" s="136">
         <v>31</v>
       </c>
-      <c r="K67" s="146">
+      <c r="K67" s="136">
         <v>31</v>
       </c>
-      <c r="L67" s="146">
+      <c r="L67" s="136">
         <v>32</v>
       </c>
-      <c r="M67" s="146">
+      <c r="M67" s="136">
         <v>33</v>
       </c>
-      <c r="N67" s="146">
+      <c r="N67" s="136">
         <v>33</v>
       </c>
-      <c r="O67" s="146">
+      <c r="O67" s="136">
         <v>34</v>
       </c>
-      <c r="P67" s="146">
+      <c r="P67" s="136">
         <v>35</v>
       </c>
-      <c r="Q67" s="146">
+      <c r="Q67" s="136">
         <v>37</v>
       </c>
-      <c r="R67" s="146">
+      <c r="R67" s="136">
         <v>39</v>
       </c>
-      <c r="S67" s="146">
+      <c r="S67" s="136">
         <v>41</v>
       </c>
-      <c r="T67" s="147">
+      <c r="T67" s="137">
         <v>48</v>
       </c>
-      <c r="U67" s="152">
+      <c r="U67" s="142">
         <f>AVERAGE(E67:T67)</f>
         <v>34.1875</v>
       </c>
-      <c r="V67" s="130">
+      <c r="V67" s="120">
         <f t="shared" si="10"/>
         <v>30.768750000000001</v>
       </c>
-      <c r="W67" s="131">
+      <c r="W67" s="121">
         <f t="shared" si="11"/>
         <v>37.606250000000003</v>
       </c>
-      <c r="X67" s="156">
+      <c r="X67" s="146">
         <f>AVERAGEIFS(E67:T67,E67:T67,"&gt;"&amp;V67, E67:T67, "&lt;"&amp;W67)</f>
         <v>32.5</v>
       </c>
-      <c r="Y67" s="132">
+      <c r="Y67" s="122">
         <f t="shared" si="13"/>
         <v>29.25</v>
       </c>
-      <c r="Z67" s="133">
+      <c r="Z67" s="123">
         <f t="shared" si="14"/>
         <v>35.75</v>
       </c>
     </row>
     <row r="68" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D68" s="122" t="s">
+      <c r="D68" s="112" t="s">
         <v>27</v>
       </c>
-      <c r="E68" s="145">
-        <v>30</v>
-      </c>
-      <c r="F68" s="146">
+      <c r="E68" s="135">
+        <v>30</v>
+      </c>
+      <c r="F68" s="136">
         <v>32</v>
       </c>
-      <c r="G68" s="146">
+      <c r="G68" s="136">
         <v>32</v>
       </c>
-      <c r="H68" s="146">
+      <c r="H68" s="136">
         <v>32</v>
       </c>
-      <c r="I68" s="146">
+      <c r="I68" s="136">
         <v>32</v>
       </c>
-      <c r="J68" s="146">
+      <c r="J68" s="136">
         <v>33</v>
       </c>
-      <c r="K68" s="146">
+      <c r="K68" s="136">
         <v>33</v>
       </c>
-      <c r="L68" s="146">
+      <c r="L68" s="136">
         <v>34</v>
       </c>
-      <c r="M68" s="146">
+      <c r="M68" s="136">
         <v>34</v>
       </c>
-      <c r="N68" s="146">
+      <c r="N68" s="136">
         <v>34</v>
       </c>
-      <c r="O68" s="146">
+      <c r="O68" s="136">
         <v>34</v>
       </c>
-      <c r="P68" s="146">
+      <c r="P68" s="136">
         <v>36</v>
       </c>
-      <c r="Q68" s="146">
+      <c r="Q68" s="136">
         <v>36</v>
       </c>
-      <c r="R68" s="146">
+      <c r="R68" s="136">
         <v>37</v>
       </c>
-      <c r="S68" s="146">
+      <c r="S68" s="136">
         <v>37</v>
       </c>
-      <c r="T68" s="147">
+      <c r="T68" s="137">
         <v>41</v>
       </c>
-      <c r="U68" s="152">
+      <c r="U68" s="142">
         <f t="shared" ref="U68:U72" si="15">AVERAGE(E68:T68)</f>
         <v>34.1875</v>
       </c>
-      <c r="V68" s="130">
+      <c r="V68" s="120">
         <f t="shared" si="10"/>
         <v>30.768750000000001</v>
       </c>
-      <c r="W68" s="131">
+      <c r="W68" s="121">
         <f t="shared" si="11"/>
         <v>37.606250000000003</v>
       </c>
-      <c r="X68" s="156">
+      <c r="X68" s="146">
         <f t="shared" ref="X68:X72" si="16">AVERAGEIFS(E68:T68,E68:T68,"&gt;"&amp;V68, E68:T68, "&lt;"&amp;W68)</f>
         <v>34</v>
       </c>
-      <c r="Y68" s="132">
+      <c r="Y68" s="122">
         <f t="shared" si="13"/>
         <v>30.6</v>
       </c>
-      <c r="Z68" s="133">
+      <c r="Z68" s="123">
         <f t="shared" si="14"/>
         <v>37.400000000000006</v>
       </c>
     </row>
     <row r="69" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D69" s="122" t="s">
+      <c r="D69" s="112" t="s">
         <v>28</v>
       </c>
-      <c r="E69" s="145">
-        <v>30</v>
-      </c>
-      <c r="F69" s="146">
+      <c r="E69" s="135">
+        <v>30</v>
+      </c>
+      <c r="F69" s="136">
         <v>31</v>
       </c>
-      <c r="G69" s="146">
+      <c r="G69" s="136">
         <v>32</v>
       </c>
-      <c r="H69" s="146">
+      <c r="H69" s="136">
         <v>32</v>
       </c>
-      <c r="I69" s="146">
+      <c r="I69" s="136">
         <v>33</v>
       </c>
-      <c r="J69" s="146">
+      <c r="J69" s="136">
         <v>34</v>
       </c>
-      <c r="K69" s="146">
+      <c r="K69" s="136">
         <v>34</v>
       </c>
-      <c r="L69" s="146">
+      <c r="L69" s="136">
         <v>34</v>
       </c>
-      <c r="M69" s="146">
+      <c r="M69" s="136">
         <v>35</v>
       </c>
-      <c r="N69" s="146">
+      <c r="N69" s="136">
         <v>35</v>
       </c>
-      <c r="O69" s="146">
+      <c r="O69" s="136">
         <v>36</v>
       </c>
-      <c r="P69" s="146">
+      <c r="P69" s="136">
         <v>36</v>
       </c>
-      <c r="Q69" s="146">
+      <c r="Q69" s="136">
         <v>36</v>
       </c>
-      <c r="R69" s="146">
+      <c r="R69" s="136">
         <v>36</v>
       </c>
-      <c r="S69" s="146">
+      <c r="S69" s="136">
         <v>36</v>
       </c>
-      <c r="T69" s="147">
+      <c r="T69" s="137">
         <v>40</v>
       </c>
-      <c r="U69" s="152">
+      <c r="U69" s="142">
         <f t="shared" si="15"/>
         <v>34.375</v>
       </c>
-      <c r="V69" s="130">
+      <c r="V69" s="120">
         <f t="shared" si="10"/>
         <v>30.9375</v>
       </c>
-      <c r="W69" s="131">
+      <c r="W69" s="121">
         <f t="shared" si="11"/>
         <v>37.8125</v>
       </c>
-      <c r="X69" s="156">
+      <c r="X69" s="146">
         <f t="shared" si="16"/>
         <v>34.285714285714285</v>
       </c>
-      <c r="Y69" s="132">
+      <c r="Y69" s="122">
         <f t="shared" si="13"/>
         <v>30.857142857142858</v>
       </c>
-      <c r="Z69" s="133">
+      <c r="Z69" s="123">
         <f t="shared" si="14"/>
         <v>37.714285714285715</v>
       </c>
     </row>
     <row r="70" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D70" s="122" t="s">
+      <c r="D70" s="112" t="s">
         <v>29</v>
       </c>
-      <c r="E70" s="145">
+      <c r="E70" s="135">
         <v>33</v>
       </c>
-      <c r="F70" s="146">
+      <c r="F70" s="136">
         <v>34</v>
       </c>
-      <c r="G70" s="146">
+      <c r="G70" s="136">
         <v>35</v>
       </c>
-      <c r="H70" s="146">
+      <c r="H70" s="136">
         <v>35</v>
       </c>
-      <c r="I70" s="146">
+      <c r="I70" s="136">
         <v>35</v>
       </c>
-      <c r="J70" s="146">
+      <c r="J70" s="136">
         <v>36</v>
       </c>
-      <c r="K70" s="146">
+      <c r="K70" s="136">
         <v>36</v>
       </c>
-      <c r="L70" s="146">
+      <c r="L70" s="136">
         <v>36</v>
       </c>
-      <c r="M70" s="146">
+      <c r="M70" s="136">
         <v>36</v>
       </c>
-      <c r="N70" s="146">
+      <c r="N70" s="136">
         <v>36</v>
       </c>
-      <c r="O70" s="146">
+      <c r="O70" s="136">
         <v>37</v>
       </c>
-      <c r="P70" s="146">
+      <c r="P70" s="136">
         <v>38</v>
       </c>
-      <c r="Q70" s="146">
+      <c r="Q70" s="136">
         <v>38</v>
       </c>
-      <c r="R70" s="146">
+      <c r="R70" s="136">
         <v>39</v>
       </c>
-      <c r="S70" s="146">
+      <c r="S70" s="136">
         <v>39</v>
       </c>
-      <c r="T70" s="147">
+      <c r="T70" s="137">
         <v>40</v>
       </c>
-      <c r="U70" s="152">
+      <c r="U70" s="142">
         <f t="shared" si="15"/>
         <v>36.4375</v>
       </c>
-      <c r="V70" s="130">
+      <c r="V70" s="120">
         <f t="shared" si="10"/>
         <v>32.793750000000003</v>
       </c>
-      <c r="W70" s="131">
+      <c r="W70" s="121">
         <f t="shared" si="11"/>
         <v>40.081250000000004</v>
       </c>
-      <c r="X70" s="156">
+      <c r="X70" s="146">
         <f t="shared" si="16"/>
         <v>36.4375</v>
       </c>
-      <c r="Y70" s="132">
+      <c r="Y70" s="122">
         <f t="shared" si="13"/>
         <v>32.793750000000003</v>
       </c>
-      <c r="Z70" s="133">
+      <c r="Z70" s="123">
         <f t="shared" si="14"/>
         <v>40.081250000000004</v>
       </c>
     </row>
     <row r="71" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D71" s="122" t="s">
-        <v>30</v>
-      </c>
-      <c r="E71" s="145">
+      <c r="D71" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="E71" s="135">
         <v>32</v>
       </c>
-      <c r="F71" s="146">
+      <c r="F71" s="136">
         <v>33</v>
       </c>
-      <c r="G71" s="146">
+      <c r="G71" s="136">
         <v>33</v>
       </c>
-      <c r="H71" s="146">
+      <c r="H71" s="136">
         <v>33</v>
       </c>
-      <c r="I71" s="146">
+      <c r="I71" s="136">
         <v>34</v>
       </c>
-      <c r="J71" s="146">
+      <c r="J71" s="136">
         <v>34</v>
       </c>
-      <c r="K71" s="146">
+      <c r="K71" s="136">
         <v>34</v>
       </c>
-      <c r="L71" s="146">
+      <c r="L71" s="136">
         <v>35</v>
       </c>
-      <c r="M71" s="146">
+      <c r="M71" s="136">
         <v>36</v>
       </c>
-      <c r="N71" s="146">
+      <c r="N71" s="136">
         <v>37</v>
       </c>
-      <c r="O71" s="146">
+      <c r="O71" s="136">
         <v>37</v>
       </c>
-      <c r="P71" s="146">
+      <c r="P71" s="136">
         <v>37</v>
       </c>
-      <c r="Q71" s="146">
+      <c r="Q71" s="136">
         <v>37</v>
       </c>
-      <c r="R71" s="146">
+      <c r="R71" s="136">
         <v>38</v>
       </c>
-      <c r="S71" s="146">
+      <c r="S71" s="136">
         <v>38</v>
       </c>
-      <c r="T71" s="147">
+      <c r="T71" s="137">
         <v>39</v>
       </c>
-      <c r="U71" s="152">
+      <c r="U71" s="142">
         <f t="shared" si="15"/>
         <v>35.4375</v>
       </c>
-      <c r="V71" s="130">
+      <c r="V71" s="120">
         <f t="shared" si="10"/>
         <v>31.893750000000001</v>
       </c>
-      <c r="W71" s="131">
+      <c r="W71" s="121">
         <f t="shared" si="11"/>
         <v>38.981250000000003</v>
       </c>
-      <c r="X71" s="156">
+      <c r="X71" s="146">
         <f t="shared" si="16"/>
         <v>35.200000000000003</v>
       </c>
-      <c r="Y71" s="132">
+      <c r="Y71" s="122">
         <f t="shared" si="13"/>
         <v>31.680000000000003</v>
       </c>
-      <c r="Z71" s="133">
+      <c r="Z71" s="123">
         <f t="shared" si="14"/>
         <v>38.720000000000006</v>
       </c>
     </row>
     <row r="72" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D72" s="123" t="s">
+      <c r="D72" s="113" t="s">
         <v>31</v>
       </c>
-      <c r="E72" s="145">
+      <c r="E72" s="135">
         <v>37</v>
       </c>
-      <c r="F72" s="146">
+      <c r="F72" s="136">
         <v>39</v>
       </c>
-      <c r="G72" s="146">
+      <c r="G72" s="136">
         <v>40</v>
       </c>
-      <c r="H72" s="146">
+      <c r="H72" s="136">
         <v>41</v>
       </c>
-      <c r="I72" s="146">
+      <c r="I72" s="136">
         <v>42</v>
       </c>
-      <c r="J72" s="146">
+      <c r="J72" s="136">
         <v>42</v>
       </c>
-      <c r="K72" s="146">
+      <c r="K72" s="136">
         <v>42</v>
       </c>
-      <c r="L72" s="146">
+      <c r="L72" s="136">
         <v>42</v>
       </c>
-      <c r="M72" s="146">
+      <c r="M72" s="136">
         <v>43</v>
       </c>
-      <c r="N72" s="146">
+      <c r="N72" s="136">
         <v>43</v>
       </c>
-      <c r="O72" s="146">
+      <c r="O72" s="136">
         <v>43</v>
       </c>
-      <c r="P72" s="146">
+      <c r="P72" s="136">
         <v>43</v>
       </c>
-      <c r="Q72" s="146">
+      <c r="Q72" s="136">
         <v>44</v>
       </c>
-      <c r="R72" s="146">
+      <c r="R72" s="136">
         <v>44</v>
       </c>
-      <c r="S72" s="146">
+      <c r="S72" s="136">
         <v>44</v>
       </c>
-      <c r="T72" s="147">
+      <c r="T72" s="137">
         <v>44</v>
       </c>
-      <c r="U72" s="153">
+      <c r="U72" s="143">
         <f t="shared" si="15"/>
         <v>42.0625</v>
       </c>
-      <c r="V72" s="134">
+      <c r="V72" s="124">
         <f t="shared" si="10"/>
         <v>37.856250000000003</v>
       </c>
-      <c r="W72" s="135">
+      <c r="W72" s="125">
         <f t="shared" si="11"/>
         <v>46.268750000000004</v>
       </c>
-      <c r="X72" s="157">
+      <c r="X72" s="147">
         <f t="shared" si="16"/>
         <v>42.4</v>
       </c>
-      <c r="Y72" s="136">
+      <c r="Y72" s="126">
         <f t="shared" si="13"/>
         <v>38.159999999999997</v>
       </c>
-      <c r="Z72" s="137">
+      <c r="Z72" s="127">
         <f t="shared" si="14"/>
         <v>46.64</v>
       </c>
     </row>
     <row r="73" spans="4:26" hidden="1" x14ac:dyDescent="0.3">
-      <c r="D73" s="124" t="s">
+      <c r="D73" s="114" t="s">
         <v>165</v>
       </c>
-      <c r="E73" s="145">
+      <c r="E73" s="135">
         <v>29</v>
       </c>
-      <c r="F73" s="146">
+      <c r="F73" s="136">
         <v>31</v>
       </c>
-      <c r="G73" s="146">
+      <c r="G73" s="136">
         <v>31</v>
       </c>
-      <c r="H73" s="146">
+      <c r="H73" s="136">
         <v>31</v>
       </c>
-      <c r="I73" s="146">
+      <c r="I73" s="136">
         <v>31</v>
       </c>
-      <c r="J73" s="146">
+      <c r="J73" s="136">
         <v>31</v>
       </c>
-      <c r="K73" s="146">
+      <c r="K73" s="136">
         <v>31</v>
       </c>
-      <c r="L73" s="146">
+      <c r="L73" s="136">
         <v>32</v>
       </c>
-      <c r="M73" s="146">
+      <c r="M73" s="136">
         <v>33</v>
       </c>
-      <c r="N73" s="146">
+      <c r="N73" s="136">
         <v>33</v>
       </c>
-      <c r="O73" s="146">
+      <c r="O73" s="136">
         <v>34</v>
       </c>
-      <c r="P73" s="146">
+      <c r="P73" s="136">
         <v>35</v>
       </c>
-      <c r="Q73" s="146">
+      <c r="Q73" s="136">
         <v>37</v>
       </c>
-      <c r="R73" s="146">
+      <c r="R73" s="136">
         <v>39</v>
       </c>
-      <c r="S73" s="146">
+      <c r="S73" s="136">
         <v>41</v>
       </c>
-      <c r="T73" s="147">
+      <c r="T73" s="137">
         <v>48</v>
       </c>
-      <c r="U73" s="151">
+      <c r="U73" s="141">
         <f>AVERAGE(E73:T73)</f>
         <v>34.1875</v>
       </c>
-      <c r="V73" s="126">
+      <c r="V73" s="116">
         <f>U73*0.9</f>
         <v>30.768750000000001</v>
       </c>
-      <c r="W73" s="127">
+      <c r="W73" s="117">
         <f>U73*1.1</f>
         <v>37.606250000000003</v>
       </c>
-      <c r="X73" s="155">
+      <c r="X73" s="145">
         <f>AVERAGEIFS(E73:T73,E73:T73,"&gt;"&amp;V73, E73:T73, "&lt;"&amp;W73)</f>
         <v>32.5</v>
       </c>
-      <c r="Y73" s="128">
+      <c r="Y73" s="118">
         <f>X73*0.9</f>
         <v>29.25</v>
       </c>
-      <c r="Z73" s="129">
+      <c r="Z73" s="119">
         <f t="shared" si="14"/>
         <v>35.75</v>
       </c>
     </row>
     <row r="74" spans="4:26" hidden="1" x14ac:dyDescent="0.3">
-      <c r="D74" s="122" t="s">
+      <c r="D74" s="112" t="s">
         <v>166</v>
       </c>
-      <c r="E74" s="145">
-        <v>30</v>
-      </c>
-      <c r="F74" s="146">
+      <c r="E74" s="135">
+        <v>30</v>
+      </c>
+      <c r="F74" s="136">
         <v>31</v>
       </c>
-      <c r="G74" s="146">
+      <c r="G74" s="136">
         <v>32</v>
       </c>
-      <c r="H74" s="146">
+      <c r="H74" s="136">
         <v>32</v>
       </c>
-      <c r="I74" s="146">
+      <c r="I74" s="136">
         <v>33</v>
       </c>
-      <c r="J74" s="146">
+      <c r="J74" s="136">
         <v>33</v>
       </c>
-      <c r="K74" s="146">
+      <c r="K74" s="136">
         <v>34</v>
       </c>
-      <c r="L74" s="146">
+      <c r="L74" s="136">
         <v>34</v>
       </c>
-      <c r="M74" s="146">
+      <c r="M74" s="136">
         <v>34</v>
       </c>
-      <c r="N74" s="146">
+      <c r="N74" s="136">
         <v>34</v>
       </c>
-      <c r="O74" s="146">
+      <c r="O74" s="136">
         <v>35</v>
       </c>
-      <c r="P74" s="146">
+      <c r="P74" s="136">
         <v>35</v>
       </c>
-      <c r="Q74" s="146">
+      <c r="Q74" s="136">
         <v>36</v>
       </c>
-      <c r="R74" s="146">
+      <c r="R74" s="136">
         <v>37</v>
       </c>
-      <c r="S74" s="146">
+      <c r="S74" s="136">
         <v>38</v>
       </c>
-      <c r="T74" s="147">
+      <c r="T74" s="137">
         <v>45</v>
       </c>
-      <c r="U74" s="152">
+      <c r="U74" s="142">
         <f t="shared" ref="U74:U88" si="17">AVERAGE(E74:T74)</f>
         <v>34.5625</v>
       </c>
-      <c r="V74" s="130">
+      <c r="V74" s="120">
         <f t="shared" ref="V74:V88" si="18">U74*0.9</f>
         <v>31.106249999999999</v>
       </c>
-      <c r="W74" s="131">
+      <c r="W74" s="121">
         <f t="shared" ref="W74:W88" si="19">U74*1.1</f>
         <v>38.018750000000004</v>
       </c>
-      <c r="X74" s="156">
+      <c r="X74" s="146">
         <f t="shared" ref="X74:X88" si="20">AVERAGEIFS(E74:T74,E74:T74,"&gt;"&amp;V74, E74:T74, "&lt;"&amp;W74)</f>
         <v>34.384615384615387</v>
       </c>
-      <c r="Y74" s="132">
+      <c r="Y74" s="122">
         <f t="shared" ref="Y74:Y88" si="21">X74*0.9</f>
         <v>30.946153846153848</v>
       </c>
-      <c r="Z74" s="133">
+      <c r="Z74" s="123">
         <f t="shared" si="14"/>
         <v>37.823076923076925</v>
       </c>
     </row>
     <row r="75" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D75" s="122" t="s">
+      <c r="D75" s="112" t="s">
         <v>158</v>
       </c>
-      <c r="E75" s="145">
+      <c r="E75" s="135">
         <v>38</v>
       </c>
-      <c r="F75" s="146">
+      <c r="F75" s="136">
         <v>39</v>
       </c>
-      <c r="G75" s="146">
+      <c r="G75" s="136">
         <v>40</v>
       </c>
-      <c r="H75" s="146">
+      <c r="H75" s="136">
         <v>41</v>
       </c>
-      <c r="I75" s="146">
+      <c r="I75" s="136">
         <v>42</v>
       </c>
-      <c r="J75" s="146">
+      <c r="J75" s="136">
         <v>42</v>
       </c>
-      <c r="K75" s="146">
+      <c r="K75" s="136">
         <v>42</v>
       </c>
-      <c r="L75" s="146">
+      <c r="L75" s="136">
         <v>43</v>
       </c>
-      <c r="M75" s="146">
+      <c r="M75" s="136">
         <v>43</v>
       </c>
-      <c r="N75" s="146">
+      <c r="N75" s="136">
         <v>43</v>
       </c>
-      <c r="O75" s="146">
+      <c r="O75" s="136">
         <v>43</v>
       </c>
-      <c r="P75" s="146">
+      <c r="P75" s="136">
         <v>44</v>
       </c>
-      <c r="Q75" s="146">
+      <c r="Q75" s="136">
         <v>44</v>
       </c>
-      <c r="R75" s="146">
+      <c r="R75" s="136">
         <v>45</v>
       </c>
-      <c r="S75" s="146">
+      <c r="S75" s="136">
         <v>46</v>
       </c>
-      <c r="T75" s="147">
+      <c r="T75" s="137">
         <v>47</v>
       </c>
-      <c r="U75" s="152">
+      <c r="U75" s="142">
         <f t="shared" si="17"/>
         <v>42.625</v>
       </c>
-      <c r="V75" s="130">
+      <c r="V75" s="120">
         <f t="shared" si="18"/>
         <v>38.362500000000004</v>
       </c>
-      <c r="W75" s="131">
+      <c r="W75" s="121">
         <f t="shared" si="19"/>
         <v>46.887500000000003</v>
       </c>
-      <c r="X75" s="156">
+      <c r="X75" s="146">
         <f t="shared" si="20"/>
         <v>42.642857142857146</v>
       </c>
-      <c r="Y75" s="132">
+      <c r="Y75" s="122">
         <f t="shared" si="21"/>
         <v>38.378571428571433</v>
       </c>
-      <c r="Z75" s="133">
+      <c r="Z75" s="123">
         <f t="shared" si="14"/>
         <v>46.907142857142865</v>
       </c>
     </row>
     <row r="76" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D76" s="122" t="s">
+      <c r="D76" s="112" t="s">
         <v>159</v>
       </c>
-      <c r="E76" s="145">
+      <c r="E76" s="135">
         <v>42</v>
       </c>
-      <c r="F76" s="146">
+      <c r="F76" s="136">
         <v>46</v>
       </c>
-      <c r="G76" s="146">
+      <c r="G76" s="136">
         <v>46</v>
       </c>
-      <c r="H76" s="146">
+      <c r="H76" s="136">
         <v>46</v>
       </c>
-      <c r="I76" s="146">
+      <c r="I76" s="136">
         <v>46</v>
       </c>
-      <c r="J76" s="146">
+      <c r="J76" s="136">
         <v>47</v>
       </c>
-      <c r="K76" s="146">
+      <c r="K76" s="136">
         <v>47</v>
       </c>
-      <c r="L76" s="146">
+      <c r="L76" s="136">
         <v>48</v>
       </c>
-      <c r="M76" s="146">
+      <c r="M76" s="136">
         <v>48</v>
       </c>
-      <c r="N76" s="146">
+      <c r="N76" s="136">
         <v>48</v>
       </c>
-      <c r="O76" s="146">
+      <c r="O76" s="136">
         <v>48</v>
       </c>
-      <c r="P76" s="146">
+      <c r="P76" s="136">
         <v>48</v>
       </c>
-      <c r="Q76" s="146">
+      <c r="Q76" s="136">
         <v>49</v>
       </c>
-      <c r="R76" s="146">
+      <c r="R76" s="136">
         <v>50</v>
       </c>
-      <c r="S76" s="146">
+      <c r="S76" s="136">
         <v>50</v>
       </c>
-      <c r="T76" s="147">
+      <c r="T76" s="137">
         <v>55</v>
       </c>
-      <c r="U76" s="152">
+      <c r="U76" s="142">
         <f t="shared" si="17"/>
         <v>47.75</v>
       </c>
-      <c r="V76" s="130">
+      <c r="V76" s="120">
         <f t="shared" si="18"/>
         <v>42.975000000000001</v>
       </c>
-      <c r="W76" s="131">
+      <c r="W76" s="121">
         <f t="shared" si="19"/>
         <v>52.525000000000006</v>
       </c>
-      <c r="X76" s="156">
+      <c r="X76" s="146">
         <f t="shared" si="20"/>
         <v>47.642857142857146</v>
       </c>
-      <c r="Y76" s="132">
+      <c r="Y76" s="122">
         <f t="shared" si="21"/>
         <v>42.878571428571433</v>
       </c>
-      <c r="Z76" s="133">
+      <c r="Z76" s="123">
         <f t="shared" si="14"/>
         <v>52.407142857142865</v>
       </c>
     </row>
     <row r="77" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D77" s="122" t="s">
+      <c r="D77" s="112" t="s">
         <v>160</v>
       </c>
-      <c r="E77" s="145">
+      <c r="E77" s="135">
         <v>41</v>
       </c>
-      <c r="F77" s="146">
+      <c r="F77" s="136">
         <v>41</v>
       </c>
-      <c r="G77" s="146">
+      <c r="G77" s="136">
         <v>41</v>
       </c>
-      <c r="H77" s="146">
+      <c r="H77" s="136">
         <v>42</v>
       </c>
-      <c r="I77" s="146">
+      <c r="I77" s="136">
         <v>42</v>
       </c>
-      <c r="J77" s="146">
+      <c r="J77" s="136">
         <v>43</v>
       </c>
-      <c r="K77" s="146">
+      <c r="K77" s="136">
         <v>44</v>
       </c>
-      <c r="L77" s="146">
+      <c r="L77" s="136">
         <v>44</v>
       </c>
-      <c r="M77" s="146">
+      <c r="M77" s="136">
         <v>44</v>
       </c>
-      <c r="N77" s="146">
+      <c r="N77" s="136">
         <v>46</v>
       </c>
-      <c r="O77" s="146">
+      <c r="O77" s="136">
         <v>48</v>
       </c>
-      <c r="P77" s="146">
+      <c r="P77" s="136">
         <v>48</v>
       </c>
-      <c r="Q77" s="146">
+      <c r="Q77" s="136">
         <v>48</v>
       </c>
-      <c r="R77" s="146">
+      <c r="R77" s="136">
         <v>50</v>
       </c>
-      <c r="S77" s="146">
+      <c r="S77" s="136">
         <v>50</v>
       </c>
-      <c r="T77" s="147">
+      <c r="T77" s="137">
         <v>50</v>
       </c>
-      <c r="U77" s="152">
+      <c r="U77" s="142">
         <f t="shared" si="17"/>
         <v>45.125</v>
       </c>
-      <c r="V77" s="130">
+      <c r="V77" s="120">
         <f t="shared" si="18"/>
         <v>40.612500000000004</v>
       </c>
-      <c r="W77" s="131">
+      <c r="W77" s="121">
         <f t="shared" si="19"/>
         <v>49.637500000000003</v>
       </c>
-      <c r="X77" s="156">
+      <c r="X77" s="146">
         <f t="shared" si="20"/>
         <v>44</v>
       </c>
-      <c r="Y77" s="132">
+      <c r="Y77" s="122">
         <f t="shared" si="21"/>
         <v>39.6</v>
       </c>
-      <c r="Z77" s="133">
+      <c r="Z77" s="123">
         <f t="shared" si="14"/>
         <v>48.400000000000006</v>
       </c>
     </row>
     <row r="78" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D78" s="122" t="s">
+      <c r="D78" s="112" t="s">
         <v>161</v>
       </c>
-      <c r="E78" s="145">
+      <c r="E78" s="135">
         <v>40</v>
       </c>
-      <c r="F78" s="146">
+      <c r="F78" s="136">
         <v>41</v>
       </c>
-      <c r="G78" s="146">
+      <c r="G78" s="136">
         <v>43</v>
       </c>
-      <c r="H78" s="146">
+      <c r="H78" s="136">
         <v>43</v>
       </c>
-      <c r="I78" s="146">
+      <c r="I78" s="136">
         <v>43</v>
       </c>
-      <c r="J78" s="146">
+      <c r="J78" s="136">
         <v>44</v>
       </c>
-      <c r="K78" s="146">
+      <c r="K78" s="136">
         <v>44</v>
       </c>
-      <c r="L78" s="146">
+      <c r="L78" s="136">
         <v>45</v>
       </c>
-      <c r="M78" s="146">
+      <c r="M78" s="136">
         <v>48</v>
       </c>
-      <c r="N78" s="146">
+      <c r="N78" s="136">
         <v>48</v>
       </c>
-      <c r="O78" s="146">
+      <c r="O78" s="136">
         <v>48</v>
       </c>
-      <c r="P78" s="146">
+      <c r="P78" s="136">
         <v>48</v>
       </c>
-      <c r="Q78" s="146">
+      <c r="Q78" s="136">
         <v>49</v>
       </c>
-      <c r="R78" s="146">
+      <c r="R78" s="136">
         <v>49</v>
       </c>
-      <c r="S78" s="146">
+      <c r="S78" s="136">
         <v>50</v>
       </c>
-      <c r="T78" s="147">
+      <c r="T78" s="137">
         <v>59</v>
       </c>
-      <c r="U78" s="152">
+      <c r="U78" s="142">
         <f t="shared" si="17"/>
         <v>46.375</v>
       </c>
-      <c r="V78" s="130">
+      <c r="V78" s="120">
         <f t="shared" si="18"/>
         <v>41.737500000000004</v>
       </c>
-      <c r="W78" s="131">
+      <c r="W78" s="121">
         <f t="shared" si="19"/>
         <v>51.012500000000003</v>
       </c>
-      <c r="X78" s="156">
+      <c r="X78" s="146">
         <f t="shared" si="20"/>
         <v>46.307692307692307</v>
       </c>
-      <c r="Y78" s="132">
+      <c r="Y78" s="122">
         <f t="shared" si="21"/>
         <v>41.676923076923075</v>
       </c>
-      <c r="Z78" s="133">
+      <c r="Z78" s="123">
         <f t="shared" si="14"/>
         <v>50.938461538461539</v>
       </c>
     </row>
     <row r="79" spans="4:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D79" s="125" t="s">
+      <c r="D79" s="115" t="s">
         <v>162</v>
       </c>
-      <c r="E79" s="148">
+      <c r="E79" s="138">
         <v>39</v>
       </c>
-      <c r="F79" s="149">
+      <c r="F79" s="139">
         <v>39</v>
       </c>
-      <c r="G79" s="149">
+      <c r="G79" s="139">
         <v>41</v>
       </c>
-      <c r="H79" s="149">
+      <c r="H79" s="139">
         <v>41</v>
       </c>
-      <c r="I79" s="149">
+      <c r="I79" s="139">
         <v>43</v>
       </c>
-      <c r="J79" s="149">
+      <c r="J79" s="139">
         <v>43</v>
       </c>
-      <c r="K79" s="149">
+      <c r="K79" s="139">
         <v>43</v>
       </c>
-      <c r="L79" s="149">
+      <c r="L79" s="139">
         <v>43</v>
       </c>
-      <c r="M79" s="149">
+      <c r="M79" s="139">
         <v>43</v>
       </c>
-      <c r="N79" s="149">
+      <c r="N79" s="139">
         <v>43</v>
       </c>
-      <c r="O79" s="149">
+      <c r="O79" s="139">
         <v>44</v>
       </c>
-      <c r="P79" s="149">
+      <c r="P79" s="139">
         <v>44</v>
       </c>
-      <c r="Q79" s="149">
+      <c r="Q79" s="139">
         <v>44</v>
       </c>
-      <c r="R79" s="149">
+      <c r="R79" s="139">
         <v>44</v>
       </c>
-      <c r="S79" s="149">
+      <c r="S79" s="139">
         <v>45</v>
       </c>
-      <c r="T79" s="150">
+      <c r="T79" s="140">
         <v>45</v>
       </c>
-      <c r="U79" s="154">
+      <c r="U79" s="144">
         <f t="shared" si="17"/>
         <v>42.75</v>
       </c>
-      <c r="V79" s="138">
+      <c r="V79" s="128">
         <f t="shared" si="18"/>
         <v>38.475000000000001</v>
       </c>
-      <c r="W79" s="139">
+      <c r="W79" s="129">
         <f t="shared" si="19"/>
         <v>47.025000000000006</v>
       </c>
-      <c r="X79" s="158">
+      <c r="X79" s="148">
         <f t="shared" si="20"/>
         <v>42.75</v>
       </c>
-      <c r="Y79" s="140">
+      <c r="Y79" s="130">
         <f t="shared" si="21"/>
         <v>38.475000000000001</v>
       </c>
-      <c r="Z79" s="141">
+      <c r="Z79" s="131">
         <f t="shared" si="14"/>
         <v>47.025000000000006</v>
       </c>
@@ -15506,22 +15478,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E75:F88 G75:T89 D89:F89 L90:T90">
-    <cfRule type="cellIs" dxfId="12" priority="24" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="23" operator="lessThan">
+      <formula>$Y75</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="24" operator="greaterThan">
       <formula>$Z75</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="23" operator="lessThan">
-      <formula>$Y75</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:T41">
-    <cfRule type="cellIs" dxfId="10" priority="28" operator="greaterThan">
-      <formula>$Z4</formula>
+    <cfRule type="cellIs" dxfId="10" priority="25" operator="lessThan">
+      <formula>$V4</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="9" priority="27" operator="lessThan">
       <formula>$Y4</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="25" operator="lessThan">
-      <formula>$V4</formula>
+    <cfRule type="cellIs" dxfId="8" priority="28" operator="greaterThan">
+      <formula>$Z4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:T42">
@@ -15541,14 +15513,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E51:T88">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
+      <formula>$V51</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
       <formula>$Y51</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="greaterThan">
       <formula>$Z51</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <formula>$V51</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E51:T89">
